--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488151_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488151_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0721</v>
+        <v>-0.9444</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0489</v>
+        <v>-0.0168</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9768</v>
+        <v>-0.9276</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0476</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8608</v>
+        <v>0.8444</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0096</v>
+        <v>0.9439</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1487</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3127</v>
+        <v>-1.1907</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5246</v>
+        <v>-1.3287</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2119</v>
+        <v>0.138</v>
       </c>
       <c r="G4" t="n">
         <v>-1.6887</v>
@@ -766,13 +766,13 @@
         <v>0.3706</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0055</v>
+        <v>0.1275</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2243</v>
+        <v>0.1505</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.471</v>
+        <v>-1.4125</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7295</v>
+        <v>-0.3263</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7415</v>
+        <v>-1.0862</v>
       </c>
       <c r="G5" t="n">
         <v>0.5721000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1167</v>
+        <v>-0.0581</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2773</v>
+        <v>0.1259</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1606</v>
+        <v>-0.1841</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6294</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>S. VICENTE GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2701</v>
+        <v>-2.4279</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1496</v>
+        <v>0.2166</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4197</v>
+        <v>-2.6445</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2499</v>
+        <v>-1.5259</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9198</v>
+        <v>0.2467</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3301</v>
+        <v>-1.7726</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.5909</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7514999999999999</v>
+        <v>1.1809</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0014</v>
+        <v>-2.1168</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.6713</v>
+        <v>-0.9343</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3301</v>
+        <v>-1.1826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.279</v>
+        <v>-0.7548</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3246</v>
+        <v>-0.3743</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6036</v>
+        <v>-0.3805</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. CATALDO</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8326</v>
+        <v>-2.4353</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.699</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1337</v>
+        <v>-2.3459</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.1367</v>
+        <v>-1.2499</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.4348</v>
+        <v>-0.9198</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2981</v>
+        <v>-0.3301</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1293</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2122</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.0074</v>
+        <v>-2.0014</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.2225</v>
+        <v>-1.6713</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2152</v>
+        <v>-0.3301</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1117</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8217</v>
+        <v>-0.4443</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4303</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3914</v>
+        <v>-0.5298</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCIA</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9427</v>
+        <v>-3.3503</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1751</v>
+        <v>-1.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7676</v>
+        <v>-1.6503</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5259</v>
+        <v>-0.8071</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2467</v>
+        <v>-0.5443</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7726</v>
+        <v>-0.2628</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5909</v>
+        <v>1.3769</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1809</v>
+        <v>1.4171</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.59</v>
+        <v>-0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1168</v>
+        <v>-2.184</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9343</v>
+        <v>-1.9614</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1826</v>
+        <v>-0.2226</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1117</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R8" t="n">
         <v>1.1117</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2697</v>
+        <v>-0.2462</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.766</v>
+        <v>0.0174</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5036</v>
+        <v>-0.2636</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2589</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>B. CATALDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8556</v>
+        <v>-3.5384</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.469</v>
+        <v>-2.1339</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3866</v>
+        <v>-1.4045</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3545</v>
+        <v>-4.1367</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9951</v>
+        <v>-4.4348</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6405</v>
+        <v>0.2981</v>
       </c>
       <c r="J9" t="n">
-        <v>1.697</v>
+        <v>-2.1293</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4422</v>
+        <v>-2.2122</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2548</v>
+        <v>0.0829</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.0515</v>
+        <v>-2.0074</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4373</v>
+        <v>-2.2225</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6143</v>
+        <v>0.2152</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.7793</v>
+        <v>1.1117</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5927</v>
+        <v>0.116</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5397</v>
+        <v>-0.0046</v>
       </c>
       <c r="U9" t="n">
-        <v>0.053</v>
+        <v>0.1206</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3144</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.4456</v>
+        <v>-4.3535</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6476</v>
+        <v>-1.7945</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7981</v>
+        <v>-2.5589</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8071</v>
+        <v>-1.3545</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5443</v>
+        <v>-1.9951</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2628</v>
+        <v>0.6405</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3769</v>
+        <v>1.697</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4171</v>
+        <v>0.4422</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0402</v>
+        <v>1.2548</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.184</v>
+        <v>-3.0515</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9614</v>
+        <v>-2.4373</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2226</v>
+        <v>-0.6143</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6676</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3415</v>
+        <v>0.0948</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9302</v>
+        <v>0.2142</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4114</v>
+        <v>-0.1194</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6294</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2019</v>
+        <v>-4.4606</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1405</v>
+        <v>-3.5962</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0614</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7033</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6457</v>
+        <v>-0.9044</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8754</v>
+        <v>-0.3311</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7703</v>
+        <v>-0.5733</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0818</v>
+        <v>-4.9181</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8523</v>
+        <v>-1.9594</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.2295</v>
+        <v>-2.9587</v>
       </c>
       <c r="G12" t="n">
         <v>-5.1948</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6636</v>
+        <v>-0.4999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9849</v>
+        <v>-0.092</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6787</v>
+        <v>-0.4079</v>
       </c>
       <c r="V12" t="n">
         <v>1.8883</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5637</v>
+        <v>-7.0534</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3504</v>
+        <v>-4.84</v>
       </c>
       <c r="F13" t="n">
         <v>-2.2134</v>
@@ -1468,10 +1468,10 @@
         <v>2.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4676</v>
+        <v>-0.0221</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7549</v>
+        <v>0.2652</v>
       </c>
       <c r="U13" t="n">
         <v>-0.2873</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-35.0173</v>
+        <v>-34.1968</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.5012</v>
+        <v>-15.6803</v>
       </c>
       <c r="F14" t="n">
         <v>-18.5164</v>
@@ -1546,10 +1546,10 @@
         <v>12.0436</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5679</v>
+        <v>-1.7471</v>
       </c>
       <c r="T14" t="n">
-        <v>0.006399999999999739</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>-2.5743</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>J. WOJCIK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.119</v>
+        <v>8.3264</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1627</v>
+        <v>6.3958</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9562</v>
+        <v>1.9306</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1871</v>
+        <v>7.5631</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3469</v>
+        <v>2.0827</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8402</v>
+        <v>5.4804</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7918</v>
+        <v>7.7829</v>
       </c>
       <c r="K15" t="n">
-        <v>1.666</v>
+        <v>2.4947</v>
       </c>
       <c r="L15" t="n">
-        <v>2.1257</v>
+        <v>5.2882</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3953</v>
+        <v>-0.2198</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3191</v>
+        <v>-0.412</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7144</v>
+        <v>0.1922</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4823</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5613</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.4657</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2184</v>
+        <v>0.1679</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8883</v>
+        <v>0.315</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6294</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. WOJCIK</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.032</v>
+        <v>7.8996</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1999</v>
+        <v>5.771</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8321</v>
+        <v>2.1286</v>
       </c>
       <c r="G16" t="n">
-        <v>7.5631</v>
+        <v>4.1871</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0827</v>
+        <v>1.3469</v>
       </c>
       <c r="I16" t="n">
-        <v>5.4804</v>
+        <v>2.8402</v>
       </c>
       <c r="J16" t="n">
-        <v>7.7829</v>
+        <v>3.7918</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4947</v>
+        <v>1.666</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2882</v>
+        <v>2.1257</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2198</v>
+        <v>0.3953</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.412</v>
+        <v>-0.3191</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1922</v>
+        <v>0.7144</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6676</v>
+        <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3392</v>
+        <v>0.342</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2699</v>
+        <v>0.388</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0694</v>
+        <v>-0.046</v>
       </c>
       <c r="V16" t="n">
-        <v>0.315</v>
+        <v>1.8883</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.5177</v>
       </c>
       <c r="X16" t="n">
-        <v>0.315</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6995</v>
+        <v>5.7203</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2351</v>
+        <v>2.9206</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4644</v>
+        <v>2.7997</v>
       </c>
       <c r="G17" t="n">
         <v>6.1229</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1325</v>
+        <v>0.1533</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7113</v>
+        <v>-0.0258</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8438</v>
+        <v>0.179</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.6622</v>
+        <v>4.5422</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4075</v>
+        <v>1.2686</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2547</v>
+        <v>3.2737</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5607</v>
+        <v>1.9868</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0875</v>
+        <v>0.5443</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6482</v>
+        <v>1.4425</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5175</v>
+        <v>1.2001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.9099</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5866</v>
+        <v>0.2903</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9568</v>
+        <v>0.7866</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0184</v>
+        <v>-0.3656</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0616</v>
+        <v>1.1522</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>2.2234</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9342</v>
+        <v>0.3146</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5756</v>
+        <v>0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3586</v>
+        <v>0.2636</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3144</v>
+        <v>0.9439</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3144</v>
+        <v>0.9439</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.4191</v>
+        <v>4.0679</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2686</v>
+        <v>4.6364</v>
       </c>
       <c r="F19" t="n">
-        <v>3.1505</v>
+        <v>-0.5685</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9868</v>
+        <v>4.2327</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5443</v>
+        <v>-0.1863</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4425</v>
+        <v>4.419</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2001</v>
+        <v>5.3582</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9099</v>
+        <v>1.4386</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2903</v>
+        <v>3.9197</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7866</v>
+        <v>-1.1255</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3656</v>
+        <v>-1.6248</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1522</v>
+        <v>0.4993</v>
       </c>
       <c r="P19" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2234</v>
+        <v>1.297</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1915</v>
+        <v>0.4085</v>
       </c>
       <c r="T19" t="n">
-        <v>0.051</v>
+        <v>0.2046</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1405</v>
+        <v>0.2039</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9439</v>
+        <v>-0.9439</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9439</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.4311</v>
+        <v>3.9028</v>
       </c>
       <c r="E20" t="n">
-        <v>4.0488</v>
+        <v>2.722</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6177</v>
+        <v>1.1808</v>
       </c>
       <c r="G20" t="n">
-        <v>4.2327</v>
+        <v>0.5607</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1863</v>
+        <v>-1.0875</v>
       </c>
       <c r="I20" t="n">
-        <v>4.419</v>
+        <v>1.6482</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3582</v>
+        <v>1.5175</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4386</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9197</v>
+        <v>1.5866</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1255</v>
+        <v>-0.9568</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6248</v>
+        <v>-1.0184</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4993</v>
+        <v>0.0616</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2283</v>
+        <v>1.1748</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>0.8901</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1547</v>
+        <v>0.2848</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9439</v>
+        <v>0.3144</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6762</v>
+        <v>2.1423</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6445</v>
+        <v>0.9383</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0317</v>
+        <v>1.204</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9275</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3228</v>
+        <v>0.1433</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0174</v>
+        <v>0.3112</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3402</v>
+        <v>-0.1679</v>
       </c>
       <c r="V21" t="n">
         <v>1.2589</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>L. MONES RIERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0809</v>
+        <v>1.1804</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2016</v>
+        <v>-0.8263</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8793</v>
+        <v>2.0067</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9726</v>
+        <v>0.8142</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5548</v>
+        <v>0.553</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4178</v>
+        <v>0.2611</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4535</v>
+        <v>-0.5844</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4636</v>
+        <v>0.0684</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.9171</v>
+        <v>-0.6529</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5191</v>
+        <v>1.3986</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0184</v>
+        <v>0.4846</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4993</v>
+        <v>0.914</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2393</v>
+        <v>-0.5602</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3231</v>
+        <v>-0.2419</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0838</v>
+        <v>-0.3184</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2583</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2583</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. MONES RIERA</t>
+          <t>A. RODRÍGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.0338</v>
+        <v>0.6441</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0221</v>
+        <v>0.6441</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0559</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8142</v>
+        <v>0.6441</v>
       </c>
       <c r="H23" t="n">
-        <v>0.553</v>
+        <v>0.6441</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5844</v>
+        <v>0.6441</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0684</v>
+        <v>0.6441</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6529</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3986</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4846</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.914</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7068</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4377</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2691</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. RODRÍGUEZ LEIRO</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,28 +2281,28 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6441</v>
+        <v>0.3221</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>J. RODRIGUEZ CAPELLIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3221</v>
+        <v>0.2141</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3221</v>
+        <v>-1.4247</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.6388</v>
       </c>
       <c r="G25" t="n">
-        <v>0.3221</v>
+        <v>2.8944</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3221</v>
+        <v>1.2216</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1.6728</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3221</v>
+        <v>1.5418</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3221</v>
+        <v>0.2147</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.3271</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.3526</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.0069</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.3457</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-0.3277</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-0.1871</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-0.1405</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CAPELLIN</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.2033</v>
+        <v>0.1503</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.6205</v>
+        <v>-0.6798</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4172</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>2.8944</v>
+        <v>-1.9726</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2216</v>
+        <v>-0.5548</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6728</v>
+        <v>-1.4178</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5418</v>
+        <v>-1.4535</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2147</v>
+        <v>0.4636</v>
       </c>
       <c r="L26" t="n">
-        <v>1.3271</v>
+        <v>-1.9171</v>
       </c>
       <c r="M26" t="n">
-        <v>1.3526</v>
+        <v>-0.5191</v>
       </c>
       <c r="N26" t="n">
-        <v>1.0069</v>
+        <v>-1.0184</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3457</v>
+        <v>0.4993</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R26" t="n">
-        <v>0.7411</v>
+        <v>1.4823</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7451</v>
+        <v>0.3087</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.383</v>
+        <v>0.4418</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3621</v>
+        <v>-0.1331</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3144</v>
+        <v>1.2583</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.2583</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.5258</v>
+        <v>-1.5264</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6307</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.8951</v>
+        <v>-0.9936</v>
       </c>
       <c r="G27" t="n">
         <v>-1.1802</v>
@@ -2560,13 +2560,13 @@
         <v>0.3706</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0868</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.0336</v>
+        <v>0.0644</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0532</v>
+        <v>-0.1517</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6294</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.3734</v>
+        <v>-2.5687</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.3452</v>
+        <v>-3.639</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9718</v>
+        <v>1.0703</v>
       </c>
       <c r="G28" t="n">
         <v>-2.4477</v>
@@ -2638,13 +2638,13 @@
         <v>1.6676</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2597</v>
+        <v>0.0644</v>
       </c>
       <c r="T28" t="n">
-        <v>0.5061</v>
+        <v>0.2124</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.2465</v>
+        <v>-0.148</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>35.0175</v>
+        <v>35.0174</v>
       </c>
       <c r="E29" t="n">
-        <v>18.5164</v>
+        <v>18.5163</v>
       </c>
       <c r="F29" t="n">
-        <v>16.501</v>
+        <v>16.5012</v>
       </c>
       <c r="G29" t="n">
         <v>22.8001</v>
@@ -2695,7 +2695,7 @@
         <v>15.9726</v>
       </c>
       <c r="L29" t="n">
-        <v>5.719799999999999</v>
+        <v>5.719800000000001</v>
       </c>
       <c r="M29" t="n">
         <v>1.1075</v>
@@ -2716,19 +2716,19 @@
         <v>17.6022</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5679</v>
+        <v>2.567899999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5742</v>
+        <v>2.5744</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.006300000000000111</v>
+        <v>-0.006400000000000045</v>
       </c>
       <c r="V29" t="n">
-        <v>4.091100000000001</v>
+        <v>4.091099999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>6.293200000000001</v>
+        <v>6.2932</v>
       </c>
       <c r="X29" t="n">
         <v>-2.2021</v>
